--- a/Agreed analysis/classification/accuracy_gap_analysis.xlsx
+++ b/Agreed analysis/classification/accuracy_gap_analysis.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>accuracy_gap_critical_difference_diagram.png</t>
+          <t>accuracy_gap_critical_difference_diagram.png/.svg</t>
         </is>
       </c>
     </row>
